--- a/06_Yetkili_Kullanıcı_Ürünler/6 - AU - PR.xlsx
+++ b/06_Yetkili_Kullanıcı_Ürünler/6 - AU - PR.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bovay\Desktop\¨¨¨¨¨¨\PROJECTS\CV TASLAK\POWER PULSE - PROJE\PLANLAMA\06 - YETKİLİ KULLANICI - PRODUCTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77A395D-2B5B-472E-8A93-A7699CC27A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D2EF64-BAE3-49D1-B9DF-16E0B73B48A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="8710" firstSheet="20" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="6. GEREKSİNİM TAKİP MATRİKSİ" sheetId="21" r:id="rId1"/>
+    <sheet name="6. GEREKSİNİM TAKİP MATRİSİ" sheetId="21" r:id="rId1"/>
     <sheet name="6.1. PRODUCT PAGE İÇERİĞİ" sheetId="1" r:id="rId2"/>
     <sheet name="6.2. PRODUCTS FILTERS İÇERİĞİ" sheetId="2" r:id="rId3"/>
     <sheet name="6.2.1. P. FİLTER ARAMA ALAN DAV" sheetId="3" r:id="rId4"/>
@@ -523,9 +523,6 @@
     <t>To the diary bağlantısı davranışı</t>
   </si>
   <si>
-    <t>6. Gerksinim Takip Matriksi</t>
-  </si>
-  <si>
     <t>RTM - 006 [AU - PR]</t>
   </si>
   <si>
@@ -651,58 +648,6 @@
     <t>Her ürün bloğunda ürünün kullanıcıya önerilip önerilmediğini gösteren öneri göstergesi bulunmalıdır.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Her ürün bloğunda ürünü tüketilen ürünler listesine eklemek için </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Add</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> düğmesi bulunmalıdır.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Her ürün bloğundaki </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="162"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Add</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> düğmesine tıklandığında ürün ekleme modalı açılmalıdır.</t>
-    </r>
-  </si>
-  <si>
     <t>Product Block Data</t>
   </si>
   <si>
@@ -731,32 +676,6 @@
   </si>
   <si>
     <t>Data Management / Functional</t>
-  </si>
-  <si>
-    <r>
-      <t>Ürün bloğundaki</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="162"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Add</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> düğmesine tıklandığında ürün ekleme modalı görüntülenmelidir.</t>
-    </r>
   </si>
   <si>
     <t>Ürün ekleme modalında tüketilecek olarak seçilen ürünün adı görüntülenmelidir.</t>
@@ -1372,6 +1291,41 @@
   </si>
   <si>
     <t>Bir onay bildirim modal penceresi görüntülenir (1), Ürünün tüketilenler listesine eklendiği görüntülenir (2)</t>
+  </si>
+  <si>
+    <t>6. Gerksinim Takip Matrisi</t>
+  </si>
+  <si>
+    <t>Her ürün bloğunda ürünü tüketilen ürünler listesine eklemek için Add butonu bulunmalıdır.</t>
+  </si>
+  <si>
+    <t>Ürün bloğundaki Add butonune tıklandığında ürün ekleme modalı görüntülenmelidir.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Her ürün bloğundaki </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="162"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Add</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> butonuna tıklandığında ürün ekleme modalı açılmalıdır.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -2440,7 +2394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="210">
+  <cellXfs count="211">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2972,6 +2926,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3530,8 +3487,8 @@
       <c r="A1" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="85" t="s">
-        <v>135</v>
+      <c r="B1" s="210" t="s">
+        <v>328</v>
       </c>
       <c r="C1" s="86"/>
       <c r="D1" s="86"/>
@@ -3542,7 +3499,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="85" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C2" s="86"/>
       <c r="F2" s="29" t="s">
@@ -3558,7 +3515,7 @@
         <v>116</v>
       </c>
       <c r="B3" s="87" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C3" s="87"/>
       <c r="D3" s="87"/>
@@ -3575,7 +3532,7 @@
         <v>118</v>
       </c>
       <c r="B4" s="87" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C4" s="87"/>
       <c r="F4" s="27" t="s">
@@ -3598,7 +3555,7 @@
         <v>122</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D7" s="31" t="s">
         <v>123</v>
@@ -3618,1198 +3575,1198 @@
     </row>
     <row r="8" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="49" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B8" s="48" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" s="48" t="s">
         <v>143</v>
-      </c>
-      <c r="C8" s="48" t="s">
-        <v>144</v>
       </c>
       <c r="D8" s="48" t="s">
         <v>94</v>
       </c>
       <c r="E8" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F8" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G8" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H8" s="48" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="78" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="49" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B9" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C9" s="48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D9" s="48" t="s">
         <v>94</v>
       </c>
       <c r="E9" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F9" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G9" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H9" s="48" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="49" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B10" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C10" s="48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D10" s="48" t="s">
         <v>94</v>
       </c>
       <c r="E10" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F10" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G10" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H10" s="48" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="76" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B11" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C11" s="48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D11" s="48" t="s">
         <v>94</v>
       </c>
       <c r="E11" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F11" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G11" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H11" s="48" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="93.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B12" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C12" s="48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D12" s="48" t="s">
         <v>94</v>
       </c>
       <c r="E12" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F12" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G12" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H12" s="48" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="49" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D13" s="48" t="s">
         <v>94</v>
       </c>
       <c r="E13" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F13" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G13" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H13" s="48" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="105.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="49" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B14" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C14" s="48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D14" s="48" t="s">
         <v>95</v>
       </c>
       <c r="E14" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F14" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G14" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H14" s="48" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="86.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="49" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B15" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C15" s="48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D15" s="48" t="s">
         <v>95</v>
       </c>
       <c r="E15" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F15" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G15" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H15" s="48" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="85.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="49" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B16" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D16" s="48" t="s">
         <v>95</v>
       </c>
       <c r="E16" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F16" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G16" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H16" s="48" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="111.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="B17" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="C17" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="B17" s="48" t="s">
-        <v>146</v>
-      </c>
-      <c r="C17" s="32" t="s">
+      <c r="D17" s="50" t="s">
         <v>157</v>
-      </c>
-      <c r="D17" s="50" t="s">
-        <v>158</v>
       </c>
       <c r="E17" s="32" t="s">
         <v>96</v>
       </c>
       <c r="F17" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G17" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H17" s="48" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="127.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="46" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B18" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C18" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="D18" s="50" t="s">
         <v>157</v>
-      </c>
-      <c r="D18" s="50" t="s">
-        <v>158</v>
       </c>
       <c r="E18" s="32" t="s">
         <v>97</v>
       </c>
       <c r="F18" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G18" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H18" s="48" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="150.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="46" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B19" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C19" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="D19" s="50" t="s">
         <v>157</v>
-      </c>
-      <c r="D19" s="50" t="s">
-        <v>158</v>
       </c>
       <c r="E19" s="32" t="s">
         <v>98</v>
       </c>
       <c r="F19" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G19" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H19" s="48" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="109" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="B20" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="C20" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="D20" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B20" s="48" t="s">
-        <v>146</v>
-      </c>
-      <c r="C20" s="48" t="s">
-        <v>144</v>
-      </c>
-      <c r="D20" s="48" t="s">
-        <v>162</v>
-      </c>
       <c r="E20" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F20" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G20" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H20" s="48" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="46" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B21" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C21" s="48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D21" s="48" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E21" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F21" s="48" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="G21" s="48" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="H21" s="48" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="46" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B22" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D22" s="48" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E22" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F22" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G22" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H22" s="48" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="85.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="46" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B23" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C23" s="48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D23" s="48" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E23" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F23" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G23" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H23" s="48" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="115" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="46" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B24" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C24" s="48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D24" s="48" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E24" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F24" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G24" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H24" s="48" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="109" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="46" t="s">
-        <v>167</v>
+        <v>329</v>
       </c>
       <c r="B25" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C25" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="D25" s="48" t="s">
+        <v>161</v>
+      </c>
+      <c r="E25" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="F25" s="48" t="s">
+        <v>312</v>
+      </c>
+      <c r="G25" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="H25" s="48" t="s">
         <v>144</v>
-      </c>
-      <c r="D25" s="48" t="s">
-        <v>162</v>
-      </c>
-      <c r="E25" s="50" t="s">
-        <v>158</v>
-      </c>
-      <c r="F25" s="48" t="s">
-        <v>316</v>
-      </c>
-      <c r="G25" s="50" t="s">
-        <v>158</v>
-      </c>
-      <c r="H25" s="48" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="85.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="46" t="s">
-        <v>168</v>
+        <v>331</v>
       </c>
       <c r="B26" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C26" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="D26" s="48" t="s">
+        <v>161</v>
+      </c>
+      <c r="E26" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="F26" s="48" t="s">
+        <v>312</v>
+      </c>
+      <c r="G26" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="H26" s="48" t="s">
         <v>144</v>
-      </c>
-      <c r="D26" s="48" t="s">
-        <v>162</v>
-      </c>
-      <c r="E26" s="50" t="s">
-        <v>158</v>
-      </c>
-      <c r="F26" s="48" t="s">
-        <v>316</v>
-      </c>
-      <c r="G26" s="50" t="s">
-        <v>158</v>
-      </c>
-      <c r="H26" s="48" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="151" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="47" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B27" s="51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C27" s="52" t="s">
+        <v>156</v>
+      </c>
+      <c r="D27" s="53" t="s">
         <v>157</v>
-      </c>
-      <c r="D27" s="53" t="s">
-        <v>158</v>
       </c>
       <c r="E27" s="28" t="s">
         <v>101</v>
       </c>
       <c r="F27" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G27" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H27" s="32" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="100" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="46" t="s">
-        <v>179</v>
+        <v>330</v>
       </c>
       <c r="B28" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C28" s="48" t="s">
+        <v>156</v>
+      </c>
+      <c r="D28" s="53" t="s">
         <v>157</v>
-      </c>
-      <c r="D28" s="53" t="s">
-        <v>158</v>
       </c>
       <c r="E28" s="48" t="s">
         <v>102</v>
       </c>
       <c r="F28" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G28" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H28" s="48" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="151.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="54" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B29" s="51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C29" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="D29" s="53" t="s">
         <v>157</v>
-      </c>
-      <c r="D29" s="53" t="s">
-        <v>158</v>
       </c>
       <c r="E29" s="51" t="s">
         <v>102</v>
       </c>
       <c r="F29" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G29" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H29" s="51" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="67" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="46" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B30" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C30" s="48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D30" s="48" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E30" s="53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F30" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G30" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H30" s="48" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="103.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="46" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B31" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C31" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="D31" s="48" t="s">
+        <v>177</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>157</v>
+      </c>
+      <c r="F31" s="48" t="s">
+        <v>312</v>
+      </c>
+      <c r="G31" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="H31" s="48" t="s">
         <v>144</v>
-      </c>
-      <c r="D31" s="48" t="s">
-        <v>181</v>
-      </c>
-      <c r="E31" s="53" t="s">
-        <v>158</v>
-      </c>
-      <c r="F31" s="48" t="s">
-        <v>316</v>
-      </c>
-      <c r="G31" s="50" t="s">
-        <v>158</v>
-      </c>
-      <c r="H31" s="48" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="103" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="46" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B32" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C32" s="48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D32" s="48" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E32" s="53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F32" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G32" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H32" s="48" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="49" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B33" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C33" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="D33" s="48" t="s">
+        <v>177</v>
+      </c>
+      <c r="E33" s="53" t="s">
+        <v>157</v>
+      </c>
+      <c r="F33" s="48" t="s">
+        <v>312</v>
+      </c>
+      <c r="G33" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="H33" s="48" t="s">
         <v>144</v>
-      </c>
-      <c r="D33" s="48" t="s">
-        <v>181</v>
-      </c>
-      <c r="E33" s="53" t="s">
-        <v>158</v>
-      </c>
-      <c r="F33" s="48" t="s">
-        <v>316</v>
-      </c>
-      <c r="G33" s="50" t="s">
-        <v>158</v>
-      </c>
-      <c r="H33" s="48" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="85.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="49" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B34" s="48" t="s">
+        <v>142</v>
+      </c>
+      <c r="C34" s="48" t="s">
         <v>143</v>
       </c>
-      <c r="C34" s="48" t="s">
+      <c r="D34" s="48" t="s">
+        <v>177</v>
+      </c>
+      <c r="E34" s="53" t="s">
+        <v>157</v>
+      </c>
+      <c r="F34" s="48" t="s">
+        <v>312</v>
+      </c>
+      <c r="G34" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="H34" s="48" t="s">
         <v>144</v>
-      </c>
-      <c r="D34" s="48" t="s">
-        <v>181</v>
-      </c>
-      <c r="E34" s="53" t="s">
-        <v>158</v>
-      </c>
-      <c r="F34" s="48" t="s">
-        <v>316</v>
-      </c>
-      <c r="G34" s="50" t="s">
-        <v>158</v>
-      </c>
-      <c r="H34" s="48" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="78.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="55" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B35" s="51" t="s">
+        <v>142</v>
+      </c>
+      <c r="C35" s="51" t="s">
         <v>143</v>
       </c>
-      <c r="C35" s="51" t="s">
+      <c r="D35" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="E35" s="53" t="s">
+        <v>157</v>
+      </c>
+      <c r="F35" s="48" t="s">
+        <v>312</v>
+      </c>
+      <c r="G35" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="H35" s="51" t="s">
         <v>144</v>
-      </c>
-      <c r="D35" s="51" t="s">
-        <v>181</v>
-      </c>
-      <c r="E35" s="53" t="s">
-        <v>158</v>
-      </c>
-      <c r="F35" s="48" t="s">
-        <v>316</v>
-      </c>
-      <c r="G35" s="50" t="s">
-        <v>158</v>
-      </c>
-      <c r="H35" s="51" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="102" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="46" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B36" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C36" s="48" t="s">
+        <v>156</v>
+      </c>
+      <c r="D36" s="53" t="s">
         <v>157</v>
-      </c>
-      <c r="D36" s="53" t="s">
-        <v>158</v>
       </c>
       <c r="E36" s="48" t="s">
         <v>104</v>
       </c>
       <c r="F36" s="48" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="G36" s="48" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="H36" s="48" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="131" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="46" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B37" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C37" s="48" t="s">
+        <v>156</v>
+      </c>
+      <c r="D37" s="53" t="s">
         <v>157</v>
-      </c>
-      <c r="D37" s="53" t="s">
-        <v>158</v>
       </c>
       <c r="E37" s="48" t="s">
         <v>104</v>
       </c>
       <c r="F37" s="48" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="G37" s="48" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="H37" s="48" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="111.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="54" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B38" s="51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C38" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="D38" s="53" t="s">
         <v>157</v>
-      </c>
-      <c r="D38" s="53" t="s">
-        <v>158</v>
       </c>
       <c r="E38" s="51" t="s">
         <v>104</v>
       </c>
       <c r="F38" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G38" s="53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H38" s="51" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="148.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="46" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B39" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C39" s="48" t="s">
+        <v>156</v>
+      </c>
+      <c r="D39" s="53" t="s">
         <v>157</v>
-      </c>
-      <c r="D39" s="53" t="s">
-        <v>158</v>
       </c>
       <c r="E39" s="48" t="s">
         <v>105</v>
       </c>
       <c r="F39" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G39" s="53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H39" s="48" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="157" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="54" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B40" s="51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C40" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="D40" s="53" t="s">
         <v>157</v>
-      </c>
-      <c r="D40" s="53" t="s">
-        <v>158</v>
       </c>
       <c r="E40" s="51" t="s">
         <v>105</v>
       </c>
       <c r="F40" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G40" s="53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H40" s="51" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="49" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B41" s="56" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C41" s="56" t="s">
+        <v>156</v>
+      </c>
+      <c r="D41" s="53" t="s">
         <v>157</v>
-      </c>
-      <c r="D41" s="53" t="s">
-        <v>158</v>
       </c>
       <c r="E41" s="56" t="s">
         <v>106</v>
       </c>
       <c r="F41" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G41" s="53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H41" s="56" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="84" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="55" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B42" s="57" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C42" s="57" t="s">
+        <v>156</v>
+      </c>
+      <c r="D42" s="53" t="s">
         <v>157</v>
-      </c>
-      <c r="D42" s="53" t="s">
-        <v>158</v>
       </c>
       <c r="E42" s="57" t="s">
         <v>106</v>
       </c>
       <c r="F42" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G42" s="53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H42" s="57" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="49" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B43" s="56" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C43" s="56" t="s">
+        <v>156</v>
+      </c>
+      <c r="D43" s="53" t="s">
         <v>157</v>
-      </c>
-      <c r="D43" s="53" t="s">
-        <v>158</v>
       </c>
       <c r="E43" s="56" t="s">
         <v>107</v>
       </c>
       <c r="F43" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G43" s="53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H43" s="56" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="94" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="55" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B44" s="57" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C44" s="57" t="s">
+        <v>156</v>
+      </c>
+      <c r="D44" s="53" t="s">
         <v>157</v>
-      </c>
-      <c r="D44" s="53" t="s">
-        <v>158</v>
       </c>
       <c r="E44" s="57" t="s">
         <v>107</v>
       </c>
       <c r="F44" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G44" s="53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H44" s="57" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="131" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="49" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B45" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C45" s="48" t="s">
+        <v>156</v>
+      </c>
+      <c r="D45" s="53" t="s">
         <v>157</v>
-      </c>
-      <c r="D45" s="53" t="s">
-        <v>158</v>
       </c>
       <c r="E45" s="48" t="s">
         <v>108</v>
       </c>
       <c r="F45" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G45" s="53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H45" s="48" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="108" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="46" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B46" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C46" s="48" t="s">
+        <v>156</v>
+      </c>
+      <c r="D46" s="53" t="s">
         <v>157</v>
-      </c>
-      <c r="D46" s="53" t="s">
-        <v>158</v>
       </c>
       <c r="E46" s="48" t="s">
         <v>108</v>
       </c>
       <c r="F46" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G46" s="53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H46" s="48" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="78" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="49" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B47" s="48" t="s">
+        <v>142</v>
+      </c>
+      <c r="C47" s="48" t="s">
         <v>143</v>
       </c>
-      <c r="C47" s="48" t="s">
-        <v>144</v>
-      </c>
       <c r="D47" s="48" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E47" s="53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F47" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G47" s="53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H47" s="48" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="97.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="49" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B48" s="48" t="s">
+        <v>142</v>
+      </c>
+      <c r="C48" s="48" t="s">
         <v>143</v>
       </c>
-      <c r="C48" s="48" t="s">
-        <v>144</v>
-      </c>
       <c r="D48" s="48" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E48" s="53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F48" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G48" s="53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H48" s="48" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="86.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="49" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B49" s="48" t="s">
+        <v>142</v>
+      </c>
+      <c r="C49" s="48" t="s">
         <v>143</v>
       </c>
-      <c r="C49" s="48" t="s">
-        <v>144</v>
-      </c>
       <c r="D49" s="48" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E49" s="53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F49" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G49" s="53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H49" s="48" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="77" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="49" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B50" s="48" t="s">
+        <v>142</v>
+      </c>
+      <c r="C50" s="48" t="s">
         <v>143</v>
       </c>
-      <c r="C50" s="48" t="s">
+      <c r="D50" s="51" t="s">
+        <v>227</v>
+      </c>
+      <c r="E50" s="53" t="s">
+        <v>157</v>
+      </c>
+      <c r="F50" s="48" t="s">
+        <v>312</v>
+      </c>
+      <c r="G50" s="53" t="s">
+        <v>157</v>
+      </c>
+      <c r="H50" s="51" t="s">
         <v>144</v>
-      </c>
-      <c r="D50" s="51" t="s">
-        <v>231</v>
-      </c>
-      <c r="E50" s="53" t="s">
-        <v>158</v>
-      </c>
-      <c r="F50" s="48" t="s">
-        <v>316</v>
-      </c>
-      <c r="G50" s="53" t="s">
-        <v>158</v>
-      </c>
-      <c r="H50" s="51" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="58" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B51" s="48" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C51" s="48" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D51" s="32" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E51" s="32" t="s">
         <v>110</v>
       </c>
       <c r="F51" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G51" s="53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H51" s="32" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="106.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="49" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B52" s="48" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C52" s="48" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D52" s="32" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E52" s="32" t="s">
         <v>111</v>
       </c>
       <c r="F52" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G52" s="53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H52" s="32" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="109" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="49" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B53" s="48" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C53" s="48" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D53" s="32" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E53" s="32" t="s">
         <v>112</v>
       </c>
       <c r="F53" s="48" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G53" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H53" s="32" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -4846,7 +4803,7 @@
         <v>12</v>
       </c>
       <c r="D1" s="120" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E1" s="114"/>
       <c r="F1" s="114"/>
@@ -4865,7 +4822,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="110" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F2" s="111"/>
       <c r="G2" s="111"/>
@@ -4888,7 +4845,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="104" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C4" s="117"/>
       <c r="D4" s="117"/>
@@ -4948,7 +4905,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="104" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C8" s="105"/>
       <c r="D8" s="104" t="s">
@@ -4956,7 +4913,7 @@
       </c>
       <c r="E8" s="105"/>
       <c r="F8" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="17"/>
@@ -4966,15 +4923,15 @@
         <v>2</v>
       </c>
       <c r="B9" s="104" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C9" s="105"/>
       <c r="D9" s="104" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E9" s="105"/>
       <c r="F9" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="17"/>
@@ -4984,7 +4941,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="104" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C10" s="105"/>
       <c r="D10" s="104" t="s">
@@ -4992,7 +4949,7 @@
       </c>
       <c r="E10" s="105"/>
       <c r="F10" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="17"/>
@@ -5010,7 +4967,7 @@
       </c>
       <c r="E11" s="105"/>
       <c r="F11" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G11" s="16"/>
       <c r="H11" s="17"/>
@@ -5137,7 +5094,7 @@
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="98" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B3" s="98"/>
       <c r="C3" s="4"/>
@@ -5225,7 +5182,7 @@
       </c>
       <c r="B12" s="166"/>
       <c r="C12" s="59" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
@@ -5236,7 +5193,7 @@
       </c>
       <c r="B13" s="166"/>
       <c r="C13" s="59" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
@@ -5247,29 +5204,29 @@
       </c>
       <c r="B14" s="166"/>
       <c r="C14" s="59" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
     </row>
     <row r="15" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="166" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B15" s="166"/>
       <c r="C15" s="59" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
     </row>
     <row r="16" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="166" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B16" s="166"/>
       <c r="C16" s="59" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
@@ -5280,7 +5237,7 @@
       </c>
       <c r="B17" s="168"/>
       <c r="C17" s="59" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
@@ -5378,7 +5335,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="106" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F2" s="178"/>
       <c r="G2" s="178"/>
@@ -5401,7 +5358,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="104" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C4" s="117"/>
       <c r="D4" s="117"/>
@@ -5461,21 +5418,21 @@
         <v>1</v>
       </c>
       <c r="B8" s="174" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C8" s="175"/>
       <c r="D8" s="174" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E8" s="175"/>
       <c r="F8" s="68" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G8" s="66" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H8" s="81" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.35">
@@ -5483,21 +5440,21 @@
         <v>2</v>
       </c>
       <c r="B9" s="174" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C9" s="175"/>
       <c r="D9" s="174" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E9" s="175"/>
       <c r="F9" s="68" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G9" s="66" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H9" s="81" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.35">
@@ -5505,21 +5462,21 @@
         <v>3</v>
       </c>
       <c r="B10" s="174" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C10" s="175"/>
       <c r="D10" s="174" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E10" s="175"/>
       <c r="F10" s="68" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G10" s="66" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H10" s="81" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -5527,21 +5484,21 @@
         <v>4</v>
       </c>
       <c r="B11" s="174" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C11" s="175"/>
       <c r="D11" s="174" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E11" s="175"/>
       <c r="F11" s="68" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G11" s="66" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H11" s="81" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
@@ -5549,18 +5506,18 @@
         <v>5</v>
       </c>
       <c r="B12" s="174" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C12" s="175"/>
       <c r="D12" s="174" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E12" s="175"/>
       <c r="F12" s="66" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G12" s="66" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H12" s="67"/>
     </row>
@@ -5569,18 +5526,18 @@
         <v>6</v>
       </c>
       <c r="B13" s="174" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C13" s="175"/>
       <c r="D13" s="174" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E13" s="175"/>
       <c r="F13" s="66" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G13" s="66" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H13" s="67"/>
     </row>
@@ -5668,10 +5625,10 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="78" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B1" s="75" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C1" s="162"/>
       <c r="D1" s="163"/>
@@ -5683,17 +5640,17 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="78" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B2" s="76" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="75" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D2" s="76"/>
       <c r="E2" s="75" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F2" s="158"/>
       <c r="G2" s="159"/>
@@ -5701,29 +5658,29 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="78" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B3" s="76" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C3" s="75" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D3" s="76" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E3" s="75" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F3" s="158" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G3" s="159"/>
       <c r="H3" s="160"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="78" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B4" s="158" t="s">
         <v>4</v>
@@ -5737,10 +5694,10 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="78" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B5" s="145" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C5" s="145"/>
       <c r="D5" s="145"/>
@@ -5751,10 +5708,10 @@
     </row>
     <row r="6" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="146" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B6" s="194" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C6" s="195"/>
       <c r="D6" s="195"/>
@@ -5804,7 +5761,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="145" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C10" s="145"/>
       <c r="D10" s="145"/>
@@ -5815,7 +5772,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="161" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B11" s="161"/>
       <c r="C11" s="161"/>
@@ -5830,7 +5787,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="145" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C12" s="145"/>
       <c r="D12" s="145"/>
@@ -5844,7 +5801,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="145" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C13" s="145"/>
       <c r="D13" s="145"/>
@@ -5858,7 +5815,7 @@
         <v>3</v>
       </c>
       <c r="B14" s="145" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C14" s="145"/>
       <c r="D14" s="145"/>
@@ -5872,7 +5829,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="145" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C15" s="145"/>
       <c r="D15" s="145"/>
@@ -5895,7 +5852,7 @@
     </row>
     <row r="17" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="193" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B17" s="193"/>
       <c r="C17" s="193"/>
@@ -5937,7 +5894,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="152" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B21" s="153"/>
       <c r="C21" s="153"/>
@@ -5969,7 +5926,7 @@
     </row>
     <row r="24" spans="1:8" ht="229.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="146" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B24" s="158"/>
       <c r="C24" s="159"/>
@@ -5991,7 +5948,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="78" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B26" s="145"/>
       <c r="C26" s="145"/>
@@ -6098,7 +6055,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="110" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F2" s="111"/>
       <c r="G2" s="111"/>
@@ -6121,7 +6078,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="104" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C4" s="117"/>
       <c r="D4" s="117"/>
@@ -6149,7 +6106,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="110" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C6" s="111"/>
       <c r="D6" s="111"/>
@@ -6195,7 +6152,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="104" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C9" s="105"/>
       <c r="D9" s="106" t="s">
@@ -6203,7 +6160,7 @@
       </c>
       <c r="E9" s="107"/>
       <c r="F9" s="61" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="17"/>
@@ -6217,11 +6174,11 @@
       </c>
       <c r="C10" s="201"/>
       <c r="D10" s="202" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E10" s="203"/>
       <c r="F10" s="61" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="17"/>
@@ -6231,7 +6188,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="104" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C11" s="105"/>
       <c r="D11" s="197" t="s">
@@ -6239,7 +6196,7 @@
       </c>
       <c r="E11" s="198"/>
       <c r="F11" s="61" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G11" s="16"/>
       <c r="H11" s="17"/>
@@ -6249,7 +6206,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="104" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C12" s="199"/>
       <c r="D12" s="104" t="s">
@@ -6257,7 +6214,7 @@
       </c>
       <c r="E12" s="199"/>
       <c r="F12" s="61" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G12" s="16"/>
       <c r="H12" s="17"/>
@@ -6267,7 +6224,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="104" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C13" s="199"/>
       <c r="D13" s="104" t="s">
@@ -6275,7 +6232,7 @@
       </c>
       <c r="E13" s="199"/>
       <c r="F13" s="61" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G13" s="16"/>
       <c r="H13" s="17"/>
@@ -6381,7 +6338,7 @@
         <v>12</v>
       </c>
       <c r="D1" s="120" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E1" s="114"/>
       <c r="F1" s="114"/>
@@ -6400,7 +6357,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="110" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F2" s="111"/>
       <c r="G2" s="111"/>
@@ -6423,7 +6380,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="104" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C4" s="117"/>
       <c r="D4" s="117"/>
@@ -6437,7 +6394,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="110" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C5" s="111"/>
       <c r="D5" s="111"/>
@@ -6494,15 +6451,15 @@
         <v>1</v>
       </c>
       <c r="B9" s="104" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C9" s="105"/>
       <c r="D9" s="104" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E9" s="105"/>
       <c r="F9" s="61" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="17"/>
@@ -6512,15 +6469,15 @@
         <v>2</v>
       </c>
       <c r="B10" s="104" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C10" s="105"/>
       <c r="D10" s="104" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E10" s="105"/>
       <c r="F10" s="61" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="17"/>
@@ -6687,7 +6644,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="110" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F2" s="111"/>
       <c r="G2" s="111"/>
@@ -6710,7 +6667,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="104" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C4" s="117"/>
       <c r="D4" s="117"/>
@@ -6724,7 +6681,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="110" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C5" s="111"/>
       <c r="D5" s="111"/>
@@ -6770,7 +6727,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="104" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C8" s="105"/>
       <c r="D8" s="104" t="s">
@@ -6778,7 +6735,7 @@
       </c>
       <c r="E8" s="105"/>
       <c r="F8" s="61" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="17"/>
@@ -6788,15 +6745,15 @@
         <v>2</v>
       </c>
       <c r="B9" s="104" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C9" s="105"/>
       <c r="D9" s="104" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E9" s="105"/>
       <c r="F9" s="61" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="17"/>
@@ -6806,7 +6763,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="104" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C10" s="105"/>
       <c r="D10" s="104" t="s">
@@ -6814,7 +6771,7 @@
       </c>
       <c r="E10" s="105"/>
       <c r="F10" s="61" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="17"/>
@@ -6832,7 +6789,7 @@
       </c>
       <c r="E11" s="105"/>
       <c r="F11" s="61" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G11" s="16"/>
       <c r="H11" s="17"/>
@@ -6842,7 +6799,7 @@
         <v>5</v>
       </c>
       <c r="B12" s="104" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C12" s="105"/>
       <c r="D12" s="104" t="s">
@@ -6850,7 +6807,7 @@
       </c>
       <c r="E12" s="105"/>
       <c r="F12" s="61" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G12" s="16"/>
       <c r="H12" s="17"/>
@@ -6955,7 +6912,7 @@
         <v>12</v>
       </c>
       <c r="D1" s="120" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E1" s="114"/>
       <c r="F1" s="114"/>
@@ -6974,7 +6931,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="110" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F2" s="111"/>
       <c r="G2" s="111"/>
@@ -6997,7 +6954,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="104" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C4" s="117"/>
       <c r="D4" s="117"/>
@@ -7057,18 +7014,18 @@
         <v>1</v>
       </c>
       <c r="B8" s="104" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C8" s="105"/>
       <c r="D8" s="206" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E8" s="207"/>
       <c r="F8" s="61" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G8" s="62" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H8" s="17"/>
     </row>
@@ -7085,10 +7042,10 @@
       </c>
       <c r="E9" s="105"/>
       <c r="F9" s="61" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G9" s="62" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H9" s="17"/>
     </row>
@@ -7238,7 +7195,7 @@
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="98" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B3" s="98"/>
       <c r="C3" s="4"/>
@@ -7319,7 +7276,7 @@
       </c>
       <c r="B11" s="208"/>
       <c r="C11" s="59" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
@@ -7330,7 +7287,7 @@
       </c>
       <c r="B12" s="208"/>
       <c r="C12" s="36" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
@@ -7341,18 +7298,18 @@
       </c>
       <c r="B13" s="208"/>
       <c r="C13" s="36" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
     </row>
     <row r="14" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="208" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B14" s="208"/>
       <c r="C14" s="36" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
@@ -7471,7 +7428,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="110" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F2" s="111"/>
       <c r="G2" s="111"/>
@@ -7494,7 +7451,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="104" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C4" s="117"/>
       <c r="D4" s="117"/>
@@ -7562,7 +7519,7 @@
       </c>
       <c r="E8" s="105"/>
       <c r="F8" s="61" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="17"/>
@@ -7704,7 +7661,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="97" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B1" s="97"/>
       <c r="C1" s="97"/>
@@ -7725,7 +7682,7 @@
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="98" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B3" s="98"/>
       <c r="C3" s="4"/>
@@ -7806,18 +7763,18 @@
       </c>
       <c r="B11" s="88"/>
       <c r="C11" s="59" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
     </row>
     <row r="12" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="88" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B12" s="88"/>
       <c r="C12" s="59" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
@@ -7828,7 +7785,7 @@
       </c>
       <c r="B13" s="91"/>
       <c r="C13" s="59" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
@@ -7839,18 +7796,18 @@
       </c>
       <c r="B14" s="91"/>
       <c r="C14" s="59" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
     </row>
     <row r="15" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="91" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B15" s="91"/>
       <c r="C15" s="59" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
@@ -7861,7 +7818,7 @@
       </c>
       <c r="B16" s="88"/>
       <c r="C16" s="59" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
@@ -7966,7 +7923,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="110" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F2" s="111"/>
       <c r="G2" s="111"/>
@@ -7989,7 +7946,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="104" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C4" s="117"/>
       <c r="D4" s="117"/>
@@ -8057,7 +8014,7 @@
       </c>
       <c r="E8" s="105"/>
       <c r="F8" s="61" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="17"/>
@@ -8210,7 +8167,7 @@
         <v>12</v>
       </c>
       <c r="D1" s="120" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E1" s="114"/>
       <c r="F1" s="114"/>
@@ -8229,7 +8186,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="110" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F2" s="111"/>
       <c r="G2" s="111"/>
@@ -8252,7 +8209,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="104" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C4" s="117"/>
       <c r="D4" s="117"/>
@@ -8312,7 +8269,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="104" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C8" s="105"/>
       <c r="D8" s="104" t="s">
@@ -8320,7 +8277,7 @@
       </c>
       <c r="E8" s="105"/>
       <c r="F8" s="61" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="17"/>
@@ -8483,7 +8440,7 @@
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="98" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B3" s="98"/>
       <c r="C3" s="4"/>
@@ -8564,7 +8521,7 @@
       </c>
       <c r="B11" s="91"/>
       <c r="C11" s="36" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
@@ -8575,7 +8532,7 @@
       </c>
       <c r="B12" s="91"/>
       <c r="C12" s="36" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
@@ -8586,7 +8543,7 @@
       </c>
       <c r="B13" s="91"/>
       <c r="C13" s="36" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
@@ -8712,7 +8669,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="110" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F2" s="111"/>
       <c r="G2" s="111"/>
@@ -8801,7 +8758,7 @@
       </c>
       <c r="E8" s="105"/>
       <c r="F8" s="59" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="17"/>
@@ -8819,7 +8776,7 @@
       </c>
       <c r="E9" s="105"/>
       <c r="F9" s="59" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="17"/>
@@ -8978,7 +8935,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="110" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F2" s="111"/>
       <c r="G2" s="111"/>
@@ -9069,7 +9026,7 @@
       </c>
       <c r="E8" s="105"/>
       <c r="F8" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="17"/>
@@ -9087,7 +9044,7 @@
       </c>
       <c r="E9" s="105"/>
       <c r="F9" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="17"/>
@@ -9105,7 +9062,7 @@
       </c>
       <c r="E10" s="105"/>
       <c r="F10" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="17"/>
@@ -9253,7 +9210,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="110" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F2" s="111"/>
       <c r="G2" s="111"/>
@@ -9344,7 +9301,7 @@
       </c>
       <c r="E8" s="105"/>
       <c r="F8" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="17"/>
@@ -9519,7 +9476,7 @@
     </row>
     <row r="3" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="98" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B3" s="98"/>
       <c r="C3" s="4"/>
@@ -9591,122 +9548,122 @@
     </row>
     <row r="10" spans="1:9" s="33" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="144" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B10" s="144"/>
       <c r="C10" s="144"/>
       <c r="D10" s="144"/>
       <c r="E10" s="144"/>
       <c r="F10" s="79" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="G10" s="50" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="33" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="142" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B11" s="142"/>
       <c r="C11" s="142"/>
       <c r="D11" s="142"/>
       <c r="E11" s="142"/>
       <c r="F11" s="80" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G11" s="32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="33" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="142" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B12" s="142"/>
       <c r="C12" s="142"/>
       <c r="D12" s="142"/>
       <c r="E12" s="142"/>
       <c r="F12" s="45" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G12" s="32" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="33" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="142" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B13" s="142"/>
       <c r="C13" s="142"/>
       <c r="D13" s="142"/>
       <c r="E13" s="142"/>
       <c r="F13" s="80" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G13" s="32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="33" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="142" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B14" s="142"/>
       <c r="C14" s="142"/>
       <c r="D14" s="142"/>
       <c r="E14" s="142"/>
       <c r="F14" s="80" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G14" s="32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="33" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="142" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B15" s="142"/>
       <c r="C15" s="142"/>
       <c r="D15" s="142"/>
       <c r="E15" s="142"/>
       <c r="F15" s="80" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G15" s="32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="33" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="143" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B16" s="143"/>
       <c r="C16" s="143"/>
       <c r="D16" s="143"/>
       <c r="E16" s="143"/>
       <c r="F16" s="80" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G16" s="32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="33" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="143" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B17" s="143"/>
       <c r="C17" s="143"/>
       <c r="D17" s="143"/>
       <c r="E17" s="143"/>
       <c r="F17" s="80" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G17" s="32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="33" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
@@ -9732,7 +9689,7 @@
     </row>
     <row r="21" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="139" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B21" s="140"/>
       <c r="C21" s="140"/>
@@ -9766,445 +9723,445 @@
     </row>
     <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.4">
       <c r="A23" s="9" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B23" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C23" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D23" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E23" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F23" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G23" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.4">
       <c r="A24" s="9" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B24" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C24" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D24" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E24" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F24" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G24" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.4">
       <c r="A25" s="9" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B25" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C25" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D25" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E25" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F25" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G25" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.4">
       <c r="A26" s="9" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B26" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C26" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D26" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E26" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F26" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G26" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.4">
       <c r="A27" s="9" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B27" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C27" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D27" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E27" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F27" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G27" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.4">
       <c r="A28" s="9" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B28" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C28" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D28" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E28" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F28" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G28" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.4">
       <c r="A29" s="9" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B29" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C29" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D29" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E29" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F29" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G29" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.4">
       <c r="A30" s="9" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B30" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C30" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D30" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E30" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F30" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G30" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.4">
       <c r="A31" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D31" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E31" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F31" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G31" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.4">
       <c r="A32" s="36" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B32" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C32" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D32" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E32" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F32" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G32" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="16" x14ac:dyDescent="0.4">
       <c r="A33" s="32" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B33" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C33" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D33" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E33" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F33" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G33" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="16" x14ac:dyDescent="0.4">
       <c r="A34" s="32" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B34" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C34" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D34" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E34" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F34" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G34" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="16" x14ac:dyDescent="0.4">
       <c r="A35" s="32" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B35" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C35" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D35" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E35" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F35" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G35" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="16" x14ac:dyDescent="0.4">
       <c r="A36" s="32" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B36" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C36" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D36" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E36" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F36" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G36" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="16" x14ac:dyDescent="0.4">
       <c r="A37" s="32" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B37" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C37" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D37" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E37" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F37" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G37" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="16" x14ac:dyDescent="0.4">
       <c r="A38" s="32" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B38" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C38" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D38" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E38" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F38" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G38" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="16" x14ac:dyDescent="0.4">
       <c r="A39" s="32" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B39" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C39" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D39" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E39" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F39" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G39" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="16" x14ac:dyDescent="0.4">
       <c r="A40" s="32" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B40" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C40" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D40" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E40" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F40" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G40" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="16" x14ac:dyDescent="0.4">
       <c r="A41" s="32" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B41" s="39" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C41" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D41" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E41" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F41" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G41" s="60" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="130" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B44" s="131"/>
       <c r="C44" s="131"/>
@@ -10307,7 +10264,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="76" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C1" s="162"/>
       <c r="D1" s="163"/>
@@ -10319,17 +10276,17 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="78" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B2" s="76" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="78" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D2" s="76"/>
       <c r="E2" s="78" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F2" s="158"/>
       <c r="G2" s="159"/>
@@ -10337,29 +10294,29 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="78" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B3" s="76" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C3" s="78" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D3" s="76" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E3" s="78" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F3" s="158" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G3" s="159"/>
       <c r="H3" s="160"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="78" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B4" s="158" t="s">
         <v>4</v>
@@ -10373,10 +10330,10 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="78" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B5" s="145" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C5" s="145"/>
       <c r="D5" s="145"/>
@@ -10387,10 +10344,10 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="146" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B6" s="148" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C6" s="148"/>
       <c r="D6" s="148"/>
@@ -10440,7 +10397,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="145" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C10" s="145"/>
       <c r="D10" s="145"/>
@@ -10451,7 +10408,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="161" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B11" s="161"/>
       <c r="C11" s="161"/>
@@ -10466,7 +10423,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="145" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C12" s="145"/>
       <c r="D12" s="145"/>
@@ -10480,7 +10437,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="145" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C13" s="145"/>
       <c r="D13" s="145"/>
@@ -10494,7 +10451,7 @@
         <v>3</v>
       </c>
       <c r="B14" s="145" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C14" s="145"/>
       <c r="D14" s="145"/>
@@ -10508,7 +10465,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="145" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C15" s="145"/>
       <c r="D15" s="145"/>
@@ -10531,7 +10488,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="152" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B17" s="153"/>
       <c r="C17" s="153"/>
@@ -10573,7 +10530,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="152" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B21" s="153"/>
       <c r="C21" s="153"/>
@@ -10615,7 +10572,7 @@
     </row>
     <row r="25" spans="1:8" ht="248" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="146" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B25" s="158"/>
       <c r="C25" s="159"/>
@@ -10637,7 +10594,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="78" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B27" s="145"/>
       <c r="C27" s="145"/>
@@ -10743,7 +10700,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="110" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F2" s="111"/>
       <c r="G2" s="111"/>
@@ -10766,7 +10723,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="104" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C4" s="117"/>
       <c r="D4" s="117"/>
@@ -10826,15 +10783,15 @@
         <v>1</v>
       </c>
       <c r="B8" s="164" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C8" s="165"/>
       <c r="D8" s="164" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E8" s="165"/>
       <c r="F8" s="61" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="17"/>
@@ -10844,15 +10801,15 @@
         <v>2</v>
       </c>
       <c r="B9" s="164" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C9" s="165"/>
       <c r="D9" s="164" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E9" s="165"/>
       <c r="F9" s="61" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="17"/>
@@ -10862,15 +10819,15 @@
         <v>3</v>
       </c>
       <c r="B10" s="164" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C10" s="165"/>
       <c r="D10" s="164" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="E10" s="165"/>
       <c r="F10" s="61" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="17"/>
@@ -10880,15 +10837,15 @@
         <v>4</v>
       </c>
       <c r="B11" s="164" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C11" s="165"/>
       <c r="D11" s="164" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E11" s="165"/>
       <c r="F11" s="61" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G11" s="16"/>
       <c r="H11" s="17"/>
